--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -1518,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672220</v>
+        <v>123672683</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>90931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,25 +1530,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576066</v>
+        <v>576083</v>
       </c>
       <c r="R9" t="n">
-        <v>7055954</v>
+        <v>7056056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672683</v>
+        <v>123672220</v>
       </c>
       <c r="B10" t="n">
-        <v>90931</v>
+        <v>90966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,25 +1642,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576083</v>
+        <v>576066</v>
       </c>
       <c r="R10" t="n">
-        <v>7056056</v>
+        <v>7055954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672801</v>
+        <v>123672683</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576111</v>
+        <v>576083</v>
       </c>
       <c r="R2" t="n">
-        <v>7056017</v>
+        <v>7056056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123672279</v>
+        <v>123672801</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576069</v>
+        <v>576111</v>
       </c>
       <c r="R3" t="n">
-        <v>7055962</v>
+        <v>7056017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672431</v>
+        <v>123672259</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>56697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +921,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576058</v>
+        <v>576066</v>
       </c>
       <c r="R4" t="n">
-        <v>7056030</v>
+        <v>7055973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672837</v>
+        <v>123672431</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,14 +1076,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576127</v>
+        <v>576058</v>
       </c>
       <c r="R5" t="n">
-        <v>7056017</v>
+        <v>7056030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1146,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672159</v>
+        <v>123672220</v>
       </c>
       <c r="B6" t="n">
-        <v>79856</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,21 +1173,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576022</v>
+        <v>576066</v>
       </c>
       <c r="R6" t="n">
-        <v>7055953</v>
+        <v>7055954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1272,7 @@
         <v>123673186</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1392,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123672259</v>
+        <v>123672159</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,52 +1403,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576066</v>
+        <v>576022</v>
       </c>
       <c r="R8" t="n">
-        <v>7055973</v>
+        <v>7055953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672683</v>
+        <v>123672837</v>
       </c>
       <c r="B9" t="n">
-        <v>90931</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,38 +1515,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576083</v>
+        <v>576127</v>
       </c>
       <c r="R9" t="n">
-        <v>7056056</v>
+        <v>7056017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,6 +1596,11 @@
           <t>15:58</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1618,22 +1613,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672220</v>
+        <v>123672279</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,34 +1641,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576066</v>
+        <v>576069</v>
       </c>
       <c r="R10" t="n">
-        <v>7055954</v>
+        <v>7055962</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672683</v>
+        <v>123672259</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576083</v>
+        <v>576066</v>
       </c>
       <c r="R2" t="n">
-        <v>7056056</v>
+        <v>7055973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123672801</v>
+        <v>123672431</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576111</v>
+        <v>576058</v>
       </c>
       <c r="R3" t="n">
-        <v>7056017</v>
+        <v>7056030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672259</v>
+        <v>123672837</v>
       </c>
       <c r="B4" t="n">
-        <v>56697</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,52 +935,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576066</v>
+        <v>576127</v>
       </c>
       <c r="R4" t="n">
-        <v>7055973</v>
+        <v>7056017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1033,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672431</v>
+        <v>123673186</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,7 +1081,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576058</v>
+        <v>576086</v>
       </c>
       <c r="R5" t="n">
-        <v>7056030</v>
+        <v>7055944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672220</v>
+        <v>123672279</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1183,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576066</v>
+        <v>576069</v>
       </c>
       <c r="R6" t="n">
-        <v>7055954</v>
+        <v>7055962</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1247,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1257,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123673186</v>
+        <v>123672801</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1320,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576086</v>
+        <v>576111</v>
       </c>
       <c r="R7" t="n">
-        <v>7055944</v>
+        <v>7056017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1374,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123672159</v>
+        <v>123672220</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>90988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,21 +1422,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576022</v>
+        <v>576066</v>
       </c>
       <c r="R8" t="n">
-        <v>7055953</v>
+        <v>7055954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672837</v>
+        <v>123672159</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,39 +1534,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576127</v>
+        <v>576022</v>
       </c>
       <c r="R9" t="n">
-        <v>7056017</v>
+        <v>7055953</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,22 +1618,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672279</v>
+        <v>123672683</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>90953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,43 +1642,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576069</v>
+        <v>576083</v>
       </c>
       <c r="R10" t="n">
-        <v>7055962</v>
+        <v>7056056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672259</v>
+        <v>123672159</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576066</v>
+        <v>576022</v>
       </c>
       <c r="R2" t="n">
-        <v>7055973</v>
+        <v>7055953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +790,7 @@
         <v>123672431</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672837</v>
+        <v>123672683</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576127</v>
+        <v>576083</v>
       </c>
       <c r="R4" t="n">
-        <v>7056017</v>
+        <v>7056056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,11 +997,6 @@
           <t>15:58</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123673186</v>
+        <v>123672220</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576086</v>
+        <v>576066</v>
       </c>
       <c r="R5" t="n">
-        <v>7055944</v>
+        <v>7055954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672279</v>
+        <v>123672801</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1203,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1212,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576069</v>
+        <v>576111</v>
       </c>
       <c r="R6" t="n">
-        <v>7055962</v>
+        <v>7056017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672801</v>
+        <v>123672259</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,31 +1267,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576111</v>
+        <v>576066</v>
       </c>
       <c r="R7" t="n">
-        <v>7056017</v>
+        <v>7055973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123672220</v>
+        <v>123672279</v>
       </c>
       <c r="B8" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,34 +1397,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576066</v>
+        <v>576069</v>
       </c>
       <c r="R8" t="n">
-        <v>7055954</v>
+        <v>7055962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672159</v>
+        <v>123673186</v>
       </c>
       <c r="B9" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,34 +1514,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576022</v>
+        <v>576086</v>
       </c>
       <c r="R9" t="n">
-        <v>7055953</v>
+        <v>7055944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672683</v>
+        <v>123672837</v>
       </c>
       <c r="B10" t="n">
-        <v>90953</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,38 +1632,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576083</v>
+        <v>576127</v>
       </c>
       <c r="R10" t="n">
-        <v>7056056</v>
+        <v>7056017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,6 +1713,11 @@
           <t>15:58</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1730,12 +1730,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672683</v>
+        <v>123672220</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576083</v>
+        <v>576066</v>
       </c>
       <c r="R4" t="n">
-        <v>7056056</v>
+        <v>7055954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672220</v>
+        <v>123672683</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576066</v>
+        <v>576083</v>
       </c>
       <c r="R5" t="n">
-        <v>7055954</v>
+        <v>7056056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672159</v>
+        <v>123672683</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576022</v>
+        <v>576083</v>
       </c>
       <c r="R2" t="n">
-        <v>7055953</v>
+        <v>7056056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672220</v>
+        <v>123672259</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,28 +921,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
@@ -952,7 +966,7 @@
         <v>576066</v>
       </c>
       <c r="R4" t="n">
-        <v>7055954</v>
+        <v>7055973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672683</v>
+        <v>123672220</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1047,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576083</v>
+        <v>576066</v>
       </c>
       <c r="R5" t="n">
-        <v>7056056</v>
+        <v>7055954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672259</v>
+        <v>123672159</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,52 +1281,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576066</v>
+        <v>576022</v>
       </c>
       <c r="R7" t="n">
-        <v>7055973</v>
+        <v>7055953</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123672279</v>
+        <v>123673186</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,16 +1397,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576069</v>
+        <v>576086</v>
       </c>
       <c r="R8" t="n">
-        <v>7055962</v>
+        <v>7055944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123673186</v>
+        <v>123672279</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1519,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576086</v>
+        <v>576069</v>
       </c>
       <c r="R9" t="n">
-        <v>7055944</v>
+        <v>7055962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672683</v>
+        <v>123672837</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576083</v>
+        <v>576127</v>
       </c>
       <c r="R2" t="n">
-        <v>7056056</v>
+        <v>7056017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +768,11 @@
           <t>15:58</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123672431</v>
+        <v>123672159</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576058</v>
+        <v>576022</v>
       </c>
       <c r="R3" t="n">
-        <v>7056030</v>
+        <v>7055953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672220</v>
+        <v>123673186</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576066</v>
+        <v>576086</v>
       </c>
       <c r="R5" t="n">
-        <v>7055954</v>
+        <v>7055944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672801</v>
+        <v>123672220</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576111</v>
+        <v>576066</v>
       </c>
       <c r="R6" t="n">
-        <v>7056017</v>
+        <v>7055954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672159</v>
+        <v>123672279</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1285,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576022</v>
+        <v>576069</v>
       </c>
       <c r="R7" t="n">
-        <v>7055953</v>
+        <v>7055962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123673186</v>
+        <v>123672683</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,43 +1398,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576086</v>
+        <v>576083</v>
       </c>
       <c r="R8" t="n">
-        <v>7055944</v>
+        <v>7056056</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672279</v>
+        <v>123672431</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,7 +1534,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576069</v>
+        <v>576058</v>
       </c>
       <c r="R9" t="n">
-        <v>7055962</v>
+        <v>7056030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,7 +1620,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672837</v>
+        <v>123672801</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576127</v>
+        <v>576111</v>
       </c>
       <c r="R10" t="n">
         <v>7056017</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1730,12 +1730,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672837</v>
+        <v>123672259</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576127</v>
+        <v>576066</v>
       </c>
       <c r="R2" t="n">
-        <v>7056017</v>
+        <v>7055973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123672159</v>
+        <v>123672220</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576022</v>
+        <v>576066</v>
       </c>
       <c r="R3" t="n">
-        <v>7055953</v>
+        <v>7055954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123672259</v>
+        <v>123673186</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,40 +925,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576066</v>
+        <v>576086</v>
       </c>
       <c r="R4" t="n">
-        <v>7055973</v>
+        <v>7055944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123673186</v>
+        <v>123672431</v>
       </c>
       <c r="B5" t="n">
         <v>57491</v>
@@ -1071,7 +1071,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576086</v>
+        <v>576058</v>
       </c>
       <c r="R5" t="n">
-        <v>7055944</v>
+        <v>7056030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672220</v>
+        <v>123672801</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1173,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576066</v>
+        <v>576111</v>
       </c>
       <c r="R6" t="n">
-        <v>7055954</v>
+        <v>7056017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672279</v>
+        <v>123672837</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,16 +1295,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,19 +1315,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576069</v>
+        <v>576127</v>
       </c>
       <c r="R7" t="n">
-        <v>7055962</v>
+        <v>7056017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,12 +1389,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1498,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672431</v>
+        <v>123672279</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1529,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,7 +1549,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576058</v>
+        <v>576069</v>
       </c>
       <c r="R9" t="n">
-        <v>7056030</v>
+        <v>7055962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672801</v>
+        <v>123672159</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,39 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576111</v>
+        <v>576022</v>
       </c>
       <c r="R10" t="n">
-        <v>7056017</v>
+        <v>7055953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672259</v>
+        <v>123673186</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576066</v>
+        <v>576086</v>
       </c>
       <c r="R2" t="n">
-        <v>7055973</v>
+        <v>7055944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123673186</v>
+        <v>123672801</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -949,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576086</v>
+        <v>576111</v>
       </c>
       <c r="R4" t="n">
-        <v>7055944</v>
+        <v>7056017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672431</v>
+        <v>123672683</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,43 +1043,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576058</v>
+        <v>576083</v>
       </c>
       <c r="R5" t="n">
-        <v>7056030</v>
+        <v>7056056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672801</v>
+        <v>123672159</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576111</v>
+        <v>576022</v>
       </c>
       <c r="R6" t="n">
-        <v>7056017</v>
+        <v>7055953</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672837</v>
+        <v>123672279</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,19 +1291,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576127</v>
+        <v>576069</v>
       </c>
       <c r="R7" t="n">
-        <v>7056017</v>
+        <v>7055962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123672683</v>
+        <v>123672431</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,38 +1384,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576083</v>
+        <v>576058</v>
       </c>
       <c r="R8" t="n">
-        <v>7056056</v>
+        <v>7056030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672279</v>
+        <v>123672259</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,31 +1506,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1558,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576069</v>
+        <v>576066</v>
       </c>
       <c r="R9" t="n">
-        <v>7055962</v>
+        <v>7055973</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672159</v>
+        <v>123672837</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,34 +1636,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576022</v>
+        <v>576127</v>
       </c>
       <c r="R10" t="n">
-        <v>7055953</v>
+        <v>7056017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,12 +1730,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123672279</v>
+        <v>123672220</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576069</v>
+        <v>576066</v>
       </c>
       <c r="R2" t="n">
-        <v>7055962</v>
+        <v>7055954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123673186</v>
+        <v>123672683</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576086</v>
+        <v>576083</v>
       </c>
       <c r="R3" t="n">
-        <v>7055944</v>
+        <v>7056056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,12 +892,7 @@
         <v>123672159</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,32 +996,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123672431</v>
+        <v>123672279</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576058</v>
+        <v>576069</v>
       </c>
       <c r="R5" t="n">
-        <v>7056030</v>
+        <v>7055962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123672683</v>
+        <v>123672626</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Köråstjärnen, Köråstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576083</v>
+        <v>576093</v>
       </c>
       <c r="R6" t="n">
-        <v>7056056</v>
+        <v>7056071</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,64 +1208,50 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123672259</v>
+        <v>123672431</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576066</v>
+        <v>576058</v>
       </c>
       <c r="R7" t="n">
-        <v>7055973</v>
+        <v>7056030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,12 +1340,7 @@
         <v>123672801</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,15 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123672220</v>
+        <v>123672837</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,34 +1465,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576066</v>
+        <v>576127</v>
       </c>
       <c r="R9" t="n">
-        <v>7055954</v>
+        <v>7056017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1539,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,27 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123672837</v>
+        <v>123673186</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,19 +1602,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576127</v>
+        <v>576086</v>
       </c>
       <c r="R10" t="n">
-        <v>7056017</v>
+        <v>7055944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1656,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,15 +1676,136 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123672259</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>576066</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7055973</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13250-2025 artfynd.xlsx
+++ b/artfynd/A 13250-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672626</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672431</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672801</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672837</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123673186</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,8 +1856,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123672259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>